--- a/data/Peroxisomal_interactions_across_dbs_final.xlsx
+++ b/data/Peroxisomal_interactions_across_dbs_final.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/18b3d1ec65516a7e/UCR_Projects/Projekte/PEXInteraktom/R_notebooks/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_CB0507B30BBEA9E479FD9890E22D62B100B4A3CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE732D15-0082-9045-8FEA-EBC3118AFD71}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="780" windowWidth="26180" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -46,8 +52,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,17 +112,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -154,7 +168,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -188,6 +202,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -222,9 +237,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -397,11 +413,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I399"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -430,7 +451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>215</v>
       </c>
@@ -450,7 +471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>215</v>
       </c>
@@ -464,7 +485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>215</v>
       </c>
@@ -478,7 +499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>215</v>
       </c>
@@ -492,7 +513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>215</v>
       </c>
@@ -506,7 +527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>215</v>
       </c>
@@ -520,7 +541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>215</v>
       </c>
@@ -534,7 +555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>215</v>
       </c>
@@ -548,7 +569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>215</v>
       </c>
@@ -562,7 +583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>215</v>
       </c>
@@ -576,7 +597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>215</v>
       </c>
@@ -590,7 +611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>215</v>
       </c>
@@ -604,7 +625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>215</v>
       </c>
@@ -630,7 +651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>215</v>
       </c>
@@ -650,7 +671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>215</v>
       </c>
@@ -670,7 +691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>215</v>
       </c>
@@ -687,7 +708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>122970</v>
       </c>
@@ -701,7 +722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>122970</v>
       </c>
@@ -715,7 +736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>122970</v>
       </c>
@@ -729,7 +750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>122970</v>
       </c>
@@ -743,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>122970</v>
       </c>
@@ -757,7 +778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>122970</v>
       </c>
@@ -771,7 +792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>122970</v>
       </c>
@@ -785,7 +806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>122970</v>
       </c>
@@ -799,7 +820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>122970</v>
       </c>
@@ -813,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>122970</v>
       </c>
@@ -827,7 +848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>224</v>
       </c>
@@ -841,7 +862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>224</v>
       </c>
@@ -855,7 +876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>224</v>
       </c>
@@ -869,7 +890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>224</v>
       </c>
@@ -883,7 +904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>224</v>
       </c>
@@ -897,7 +918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>224</v>
       </c>
@@ -911,7 +932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>224</v>
       </c>
@@ -925,7 +946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>224</v>
       </c>
@@ -939,7 +960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>224</v>
       </c>
@@ -953,7 +974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>224</v>
       </c>
@@ -967,7 +988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>224</v>
       </c>
@@ -981,7 +1002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>224</v>
       </c>
@@ -995,7 +1016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>224</v>
       </c>
@@ -1009,7 +1030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>224</v>
       </c>
@@ -1023,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1962</v>
       </c>
@@ -1037,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1962</v>
       </c>
@@ -1051,7 +1072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1962</v>
       </c>
@@ -1068,7 +1089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>84188</v>
       </c>
@@ -1082,7 +1103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>84188</v>
       </c>
@@ -1096,7 +1117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>84188</v>
       </c>
@@ -1110,7 +1131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>84188</v>
       </c>
@@ -1124,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>84188</v>
       </c>
@@ -1138,7 +1159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>84188</v>
       </c>
@@ -1152,7 +1173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>55825</v>
       </c>
@@ -1166,7 +1187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>55825</v>
       </c>
@@ -1180,7 +1201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>55825</v>
       </c>
@@ -1194,7 +1215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>55825</v>
       </c>
@@ -1208,7 +1229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>55825</v>
       </c>
@@ -1222,7 +1243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55825</v>
       </c>
@@ -1236,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>55825</v>
       </c>
@@ -1250,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>55825</v>
       </c>
@@ -1264,7 +1285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>55825</v>
       </c>
@@ -1278,7 +1299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>55825</v>
       </c>
@@ -1292,7 +1313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>55825</v>
       </c>
@@ -1306,7 +1327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>55825</v>
       </c>
@@ -1320,7 +1341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>5194</v>
       </c>
@@ -1334,7 +1355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>5194</v>
       </c>
@@ -1348,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>5194</v>
       </c>
@@ -1362,7 +1383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>5194</v>
       </c>
@@ -1376,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>5194</v>
       </c>
@@ -1396,7 +1417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>5194</v>
       </c>
@@ -1416,7 +1437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>5194</v>
       </c>
@@ -1430,7 +1451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5194</v>
       </c>
@@ -1444,7 +1465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>5194</v>
       </c>
@@ -1470,7 +1491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>5194</v>
       </c>
@@ -1496,7 +1517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>5194</v>
       </c>
@@ -1510,7 +1531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>5830</v>
       </c>
@@ -1524,7 +1545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>5830</v>
       </c>
@@ -1538,7 +1559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>5830</v>
       </c>
@@ -1552,7 +1573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>5830</v>
       </c>
@@ -1578,7 +1599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>5830</v>
       </c>
@@ -1604,7 +1625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>5830</v>
       </c>
@@ -1618,7 +1639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>5830</v>
       </c>
@@ -1632,7 +1653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>5830</v>
       </c>
@@ -1646,7 +1667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>5830</v>
       </c>
@@ -1672,7 +1693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>5830</v>
       </c>
@@ -1686,7 +1707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>5830</v>
       </c>
@@ -1700,7 +1721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>5830</v>
       </c>
@@ -1720,7 +1741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>5830</v>
       </c>
@@ -1734,7 +1755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>5830</v>
       </c>
@@ -1748,7 +1769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>5830</v>
       </c>
@@ -1771,7 +1792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>5830</v>
       </c>
@@ -1785,7 +1806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>5830</v>
       </c>
@@ -1799,7 +1820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>5830</v>
       </c>
@@ -1813,7 +1834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>5830</v>
       </c>
@@ -1827,7 +1848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>5830</v>
       </c>
@@ -1841,7 +1862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>5830</v>
       </c>
@@ -1855,7 +1876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>5830</v>
       </c>
@@ -1869,7 +1890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>5830</v>
       </c>
@@ -1883,7 +1904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>5830</v>
       </c>
@@ -1897,7 +1918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>5830</v>
       </c>
@@ -1911,7 +1932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>5830</v>
       </c>
@@ -1925,7 +1946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>5830</v>
       </c>
@@ -1939,7 +1960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>5830</v>
       </c>
@@ -1953,7 +1974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5830</v>
       </c>
@@ -1967,7 +1988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>5830</v>
       </c>
@@ -1981,7 +2002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>5830</v>
       </c>
@@ -1995,7 +2016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>5830</v>
       </c>
@@ -2009,7 +2030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>5830</v>
       </c>
@@ -2023,7 +2044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>5830</v>
       </c>
@@ -2037,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>5830</v>
       </c>
@@ -2051,7 +2072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>5830</v>
       </c>
@@ -2065,7 +2086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>5830</v>
       </c>
@@ -2079,7 +2100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>5830</v>
       </c>
@@ -2093,7 +2114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>5830</v>
       </c>
@@ -2107,7 +2128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>5830</v>
       </c>
@@ -2121,7 +2142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>5830</v>
       </c>
@@ -2135,7 +2156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>5830</v>
       </c>
@@ -2149,7 +2170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>5830</v>
       </c>
@@ -2163,7 +2184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>5830</v>
       </c>
@@ -2177,7 +2198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>5830</v>
       </c>
@@ -2191,7 +2212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>5830</v>
       </c>
@@ -2205,7 +2226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>5830</v>
       </c>
@@ -2219,7 +2240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>5830</v>
       </c>
@@ -2233,7 +2254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>5830</v>
       </c>
@@ -2247,7 +2268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>5830</v>
       </c>
@@ -2261,7 +2282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>5830</v>
       </c>
@@ -2275,7 +2296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>5830</v>
       </c>
@@ -2292,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>5830</v>
       </c>
@@ -2309,7 +2330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>5830</v>
       </c>
@@ -2326,7 +2347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>5264</v>
       </c>
@@ -2340,7 +2361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>5264</v>
       </c>
@@ -2354,7 +2375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>5264</v>
       </c>
@@ -2374,7 +2395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>5264</v>
       </c>
@@ -2388,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>5264</v>
       </c>
@@ -2402,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>5264</v>
       </c>
@@ -2416,7 +2437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5264</v>
       </c>
@@ -2430,7 +2451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>5827</v>
       </c>
@@ -2444,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>5827</v>
       </c>
@@ -2458,7 +2479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>5827</v>
       </c>
@@ -2472,7 +2493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>5827</v>
       </c>
@@ -2486,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>5827</v>
       </c>
@@ -2500,7 +2521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>5827</v>
       </c>
@@ -2514,7 +2535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>5827</v>
       </c>
@@ -2528,7 +2549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>5827</v>
       </c>
@@ -2542,7 +2563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>5827</v>
       </c>
@@ -2556,7 +2577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>222659</v>
       </c>
@@ -2570,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>222659</v>
       </c>
@@ -2584,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>222659</v>
       </c>
@@ -2598,7 +2619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>222659</v>
       </c>
@@ -2612,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>222659</v>
       </c>
@@ -2626,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>10478</v>
       </c>
@@ -2646,7 +2667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>10478</v>
       </c>
@@ -2660,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>5825</v>
       </c>
@@ -2674,7 +2695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>5825</v>
       </c>
@@ -2688,7 +2709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>5825</v>
       </c>
@@ -2711,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>5825</v>
       </c>
@@ -2728,7 +2749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>51024</v>
       </c>
@@ -2742,7 +2763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>51024</v>
       </c>
@@ -2756,7 +2777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>51024</v>
       </c>
@@ -2770,7 +2791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>51024</v>
       </c>
@@ -2784,7 +2805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>51024</v>
       </c>
@@ -2798,7 +2819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>51024</v>
       </c>
@@ -2812,7 +2833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>51024</v>
       </c>
@@ -2826,7 +2847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>51024</v>
       </c>
@@ -2846,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>51024</v>
       </c>
@@ -2860,7 +2881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>51024</v>
       </c>
@@ -2874,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>51024</v>
       </c>
@@ -2888,7 +2909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>51024</v>
       </c>
@@ -2902,7 +2923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>51024</v>
       </c>
@@ -2916,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>51024</v>
       </c>
@@ -2930,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>51024</v>
       </c>
@@ -2944,7 +2965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>51024</v>
       </c>
@@ -2958,7 +2979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>51024</v>
       </c>
@@ -2972,7 +2993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>51024</v>
       </c>
@@ -2986,7 +3007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>51024</v>
       </c>
@@ -3000,7 +3021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>51024</v>
       </c>
@@ -3014,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>51024</v>
       </c>
@@ -3028,7 +3049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>51024</v>
       </c>
@@ -3042,7 +3063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>51024</v>
       </c>
@@ -3056,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>252995</v>
       </c>
@@ -3070,7 +3091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>252995</v>
       </c>
@@ -3084,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>252995</v>
       </c>
@@ -3098,7 +3119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>252995</v>
       </c>
@@ -3112,7 +3133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>252995</v>
       </c>
@@ -3126,7 +3147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>252995</v>
       </c>
@@ -3140,7 +3161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>252995</v>
       </c>
@@ -3154,7 +3175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>252995</v>
       </c>
@@ -3168,7 +3189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>252995</v>
       </c>
@@ -3182,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>5826</v>
       </c>
@@ -3202,7 +3223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>5826</v>
       </c>
@@ -3216,7 +3237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>5826</v>
       </c>
@@ -3230,7 +3251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>5826</v>
       </c>
@@ -3244,7 +3265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>8309</v>
       </c>
@@ -3258,7 +3279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>8309</v>
       </c>
@@ -3272,7 +3293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>8309</v>
       </c>
@@ -3286,7 +3307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>5052</v>
       </c>
@@ -3300,7 +3321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>5052</v>
       </c>
@@ -3314,7 +3335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>5052</v>
       </c>
@@ -3328,7 +3349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>5052</v>
       </c>
@@ -3342,7 +3363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5052</v>
       </c>
@@ -3356,7 +3377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>5052</v>
       </c>
@@ -3370,7 +3391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>5052</v>
       </c>
@@ -3384,7 +3405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>5052</v>
       </c>
@@ -3404,7 +3425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>5052</v>
       </c>
@@ -3418,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>6647</v>
       </c>
@@ -3432,7 +3453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>6647</v>
       </c>
@@ -3446,7 +3467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>6647</v>
       </c>
@@ -3460,7 +3481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>6647</v>
       </c>
@@ -3486,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>6647</v>
       </c>
@@ -3503,7 +3524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>6647</v>
       </c>
@@ -3520,7 +3541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>6647</v>
       </c>
@@ -3537,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>30</v>
       </c>
@@ -3551,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>30</v>
       </c>
@@ -3565,7 +3586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>30</v>
       </c>
@@ -3579,7 +3600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>30</v>
       </c>
@@ -3593,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>30</v>
       </c>
@@ -3607,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>30</v>
       </c>
@@ -3621,7 +3642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>30</v>
       </c>
@@ -3635,7 +3656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>30</v>
       </c>
@@ -3649,7 +3670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>30</v>
       </c>
@@ -3663,7 +3684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>30</v>
       </c>
@@ -3677,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>30</v>
       </c>
@@ -3691,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>30</v>
       </c>
@@ -3705,7 +3726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>30</v>
       </c>
@@ -3719,7 +3740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -3733,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>30</v>
       </c>
@@ -3747,7 +3768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:9">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>30</v>
       </c>
@@ -3761,7 +3782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:9">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>30</v>
       </c>
@@ -3775,7 +3796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:9">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>373156</v>
       </c>
@@ -3789,7 +3810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:9">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>373156</v>
       </c>
@@ -3803,7 +3824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:9">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>373156</v>
       </c>
@@ -3817,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:9">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>373156</v>
       </c>
@@ -3831,7 +3852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:9">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>373156</v>
       </c>
@@ -3857,7 +3878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:9">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>373156</v>
       </c>
@@ -3871,7 +3892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:9">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>373156</v>
       </c>
@@ -3885,7 +3906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:9">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>373156</v>
       </c>
@@ -3899,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:9">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>4843</v>
       </c>
@@ -3913,7 +3934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:9">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>4843</v>
       </c>
@@ -3927,7 +3948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:9">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>4843</v>
       </c>
@@ -3941,7 +3962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:9">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>4843</v>
       </c>
@@ -3955,7 +3976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:9">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>4843</v>
       </c>
@@ -3972,7 +3993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:9">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>10654</v>
       </c>
@@ -3986,7 +4007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:4">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>10654</v>
       </c>
@@ -4000,7 +4021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:4">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>10654</v>
       </c>
@@ -4014,7 +4035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:4">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>10654</v>
       </c>
@@ -4028,7 +4049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:4">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>94009</v>
       </c>
@@ -4042,7 +4063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:4">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>94009</v>
       </c>
@@ -4056,7 +4077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:4">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>219743</v>
       </c>
@@ -4070,7 +4091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:4">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>219743</v>
       </c>
@@ -4084,7 +4105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:4">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>219743</v>
       </c>
@@ -4098,7 +4119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:4">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>219743</v>
       </c>
@@ -4112,7 +4133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:4">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>219743</v>
       </c>
@@ -4126,7 +4147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:4">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>219743</v>
       </c>
@@ -4140,7 +4161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>219743</v>
       </c>
@@ -4154,7 +4175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:4">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>219743</v>
       </c>
@@ -4168,7 +4189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:4">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>219743</v>
       </c>
@@ -4182,7 +4203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:4">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>641371</v>
       </c>
@@ -4196,7 +4217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:4">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>641371</v>
       </c>
@@ -4210,7 +4231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:9">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>641371</v>
       </c>
@@ -4224,7 +4245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>641371</v>
       </c>
@@ -4238,7 +4259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:9">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>51703</v>
       </c>
@@ -4252,7 +4273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:9">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>51703</v>
       </c>
@@ -4275,7 +4296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:9">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>1610</v>
       </c>
@@ -4289,7 +4310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:9">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>1610</v>
       </c>
@@ -4303,7 +4324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:9">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>1610</v>
       </c>
@@ -4317,7 +4338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:9">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>11001</v>
       </c>
@@ -4331,7 +4352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>11001</v>
       </c>
@@ -4345,7 +4366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>11001</v>
       </c>
@@ -4359,7 +4380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:9">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>284273</v>
       </c>
@@ -4373,7 +4394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:9">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>284273</v>
       </c>
@@ -4387,7 +4408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:9">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>284273</v>
       </c>
@@ -4401,7 +4422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:9">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>284273</v>
       </c>
@@ -4415,7 +4436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:9">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>284273</v>
       </c>
@@ -4429,7 +4450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:9">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>84129</v>
       </c>
@@ -4443,7 +4464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>84129</v>
       </c>
@@ -4457,7 +4478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>91452</v>
       </c>
@@ -4471,7 +4492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>91452</v>
       </c>
@@ -4485,7 +4506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>91452</v>
       </c>
@@ -4499,7 +4520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>91452</v>
       </c>
@@ -4513,7 +4534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>91452</v>
       </c>
@@ -4527,7 +4548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>91452</v>
       </c>
@@ -4541,7 +4562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>8799</v>
       </c>
@@ -4555,7 +4576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>8799</v>
       </c>
@@ -4569,7 +4590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>8799</v>
       </c>
@@ -4595,7 +4616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>8799</v>
       </c>
@@ -4609,7 +4630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>8799</v>
       </c>
@@ -4623,7 +4644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>10005</v>
       </c>
@@ -4637,7 +4658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>10005</v>
       </c>
@@ -4651,7 +4672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>10005</v>
       </c>
@@ -4665,7 +4686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>10901</v>
       </c>
@@ -4679,7 +4700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:9">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>10901</v>
       </c>
@@ -4693,7 +4714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:9">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>10901</v>
       </c>
@@ -4707,7 +4728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:9">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>10901</v>
       </c>
@@ -4721,7 +4742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:9">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>10901</v>
       </c>
@@ -4735,7 +4756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>54363</v>
       </c>
@@ -4749,7 +4770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>54363</v>
       </c>
@@ -4763,7 +4784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:9">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>54363</v>
       </c>
@@ -4777,7 +4798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:9">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>51</v>
       </c>
@@ -4791,7 +4812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:9">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>51</v>
       </c>
@@ -4805,7 +4826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:9">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>51</v>
       </c>
@@ -4819,7 +4840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:9">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>3417</v>
       </c>
@@ -4845,7 +4866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:9">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>3417</v>
       </c>
@@ -4859,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:9">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>2182</v>
       </c>
@@ -4873,7 +4894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:9">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>23305</v>
       </c>
@@ -4890,7 +4911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:9">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>189</v>
       </c>
@@ -4916,7 +4937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:9">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>189</v>
       </c>
@@ -4930,7 +4951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>570</v>
       </c>
@@ -4944,7 +4965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>570</v>
       </c>
@@ -4958,7 +4979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>8528</v>
       </c>
@@ -4972,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>847</v>
       </c>
@@ -4995,7 +5016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>847</v>
       </c>
@@ -5009,7 +5030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>847</v>
       </c>
@@ -5023,7 +5044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>1384</v>
       </c>
@@ -5037,7 +5058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>54677</v>
       </c>
@@ -5051,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>26063</v>
       </c>
@@ -5065,7 +5086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>26063</v>
       </c>
@@ -5079,7 +5100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>3416</v>
       </c>
@@ -5093,7 +5114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>3416</v>
       </c>
@@ -5110,7 +5131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>10059</v>
       </c>
@@ -5133,7 +5154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>10059</v>
       </c>
@@ -5147,7 +5168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>10059</v>
       </c>
@@ -5167,7 +5188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>1891</v>
       </c>
@@ -5181,7 +5202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>1891</v>
       </c>
@@ -5195,7 +5216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1891</v>
       </c>
@@ -5209,7 +5230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>1891</v>
       </c>
@@ -5223,7 +5244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:7">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>1891</v>
       </c>
@@ -5237,7 +5258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>1891</v>
       </c>
@@ -5251,7 +5272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>1891</v>
       </c>
@@ -5265,7 +5286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>1891</v>
       </c>
@@ -5279,7 +5300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:7">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>2053</v>
       </c>
@@ -5299,7 +5320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>2053</v>
       </c>
@@ -5313,7 +5334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>225</v>
       </c>
@@ -5327,7 +5348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>225</v>
       </c>
@@ -5350,7 +5371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:7">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>8443</v>
       </c>
@@ -5364,7 +5385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>25824</v>
       </c>
@@ -5378,7 +5399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>25824</v>
       </c>
@@ -5395,7 +5416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>6342</v>
       </c>
@@ -5409,7 +5430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:7">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>6342</v>
       </c>
@@ -5423,7 +5444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:9">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>6342</v>
       </c>
@@ -5437,7 +5458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:9">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>6342</v>
       </c>
@@ -5451,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:9">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>6342</v>
       </c>
@@ -5465,7 +5486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:9">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>6342</v>
       </c>
@@ -5482,7 +5503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:9">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>6648</v>
       </c>
@@ -5496,7 +5517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:9">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>6648</v>
       </c>
@@ -5519,7 +5540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:9">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>54996</v>
       </c>
@@ -5533,7 +5554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:9">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>26061</v>
       </c>
@@ -5559,7 +5580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:9">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>26061</v>
       </c>
@@ -5573,7 +5594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:9">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>51179</v>
       </c>
@@ -5587,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:9">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>3155</v>
       </c>
@@ -5601,7 +5622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>3155</v>
       </c>
@@ -5615,7 +5636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:9">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>3155</v>
       </c>
@@ -5629,7 +5650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:9">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>51268</v>
       </c>
@@ -5643,7 +5664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:9">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>3295</v>
       </c>
@@ -5657,7 +5678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:9">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>3295</v>
       </c>
@@ -5671,7 +5692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:9">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>3295</v>
       </c>
@@ -5685,7 +5706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:9">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>4598</v>
       </c>
@@ -5711,7 +5732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:9">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>3422</v>
       </c>
@@ -5725,7 +5746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:9">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>23417</v>
       </c>
@@ -5745,7 +5766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:9">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>23417</v>
       </c>
@@ -5759,7 +5780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:9">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>4358</v>
       </c>
@@ -5773,7 +5794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:9">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>83594</v>
       </c>
@@ -5787,7 +5808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:9">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>10455</v>
       </c>
@@ -5801,7 +5822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:9">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>56947</v>
       </c>
@@ -5824,7 +5845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:9">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>5189</v>
       </c>
@@ -5838,7 +5859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:9">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>5189</v>
       </c>
@@ -5858,7 +5879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:9">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>5824</v>
       </c>
@@ -5881,7 +5902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:9">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>5824</v>
       </c>
@@ -5895,7 +5916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="366" spans="1:9">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>5824</v>
       </c>
@@ -5921,7 +5942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="367" spans="1:9">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>5824</v>
       </c>
@@ -5935,7 +5956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="368" spans="1:9">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>5824</v>
       </c>
@@ -5949,7 +5970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:9">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>5824</v>
       </c>
@@ -5963,7 +5984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:9">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>5824</v>
       </c>
@@ -5977,7 +5998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:9">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>5824</v>
       </c>
@@ -6000,7 +6021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:9">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>5824</v>
       </c>
@@ -6026,7 +6047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:9">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>5824</v>
       </c>
@@ -6049,7 +6070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:9">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>5824</v>
       </c>
@@ -6078,7 +6099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:9">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>5824</v>
       </c>
@@ -6092,7 +6113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:9">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>5824</v>
       </c>
@@ -6106,7 +6127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:9">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>5824</v>
       </c>
@@ -6135,7 +6156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:9">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>5824</v>
       </c>
@@ -6149,7 +6170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:9">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>5824</v>
       </c>
@@ -6169,7 +6190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:9">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>5190</v>
       </c>
@@ -6183,7 +6204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:9">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>5190</v>
       </c>
@@ -6203,7 +6224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:9">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>5192</v>
       </c>
@@ -6223,7 +6244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:9">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>5192</v>
       </c>
@@ -6237,7 +6258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:9">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>5192</v>
       </c>
@@ -6260,7 +6281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:9">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>5193</v>
       </c>
@@ -6274,7 +6295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:9">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>5193</v>
       </c>
@@ -6288,7 +6309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:9">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>5193</v>
       </c>
@@ -6302,7 +6323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:9">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>5193</v>
       </c>
@@ -6316,7 +6337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:9">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>9409</v>
       </c>
@@ -6330,7 +6351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:9">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>9409</v>
       </c>
@@ -6344,7 +6365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:9">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>9409</v>
       </c>
@@ -6370,7 +6391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:9">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>9409</v>
       </c>
@@ -6384,7 +6405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:9">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>92960</v>
       </c>
@@ -6398,7 +6419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:9">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>92960</v>
       </c>
@@ -6412,7 +6433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:9">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>92960</v>
       </c>
@@ -6426,7 +6447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:9">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>55670</v>
       </c>
@@ -6446,7 +6467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:9">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>55670</v>
       </c>
@@ -6463,7 +6484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:9">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>5191</v>
       </c>
@@ -6477,7 +6498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:9">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>5195</v>
       </c>
